--- a/customer_service_forms/042_glymed_for_you--customer_service_forms.xlsx
+++ b/customer_service_forms/042_glymed_for_you--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_service_forms</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>skin_care_quiz</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to fill out this form to help us improve our skincare services</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,107 +547,127 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_service_forms</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your experience with our skincare services?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate the quality of our skincare services?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Have you ever had a problem with our skincare services?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>improvement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What would you like to see improved in our skincare services?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please type your answer</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Any additional comments or feedback?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please type your answer</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,46 +677,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>visit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How often do you visit our skincare services?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How likely are you to recommend our skincare services to a friend or family member?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,156 +736,184 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>products</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What do you think about our skincare products?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>purchased</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Have you ever purchased our skincare products?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>repurchase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How likely are you to repurchase our skincare products?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Do you think our skincare services are value for money?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What do you think about our customer service?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>problem_customer_service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Have you ever had a problem with our customer service?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What do you think about our skincare services in comparison to others?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,246 +925,74 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>use_again</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>How likely are you to use our skincare services again?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please select one of the options below</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>new_services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Would you like to see any new services or features in our skincare services?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please type your answer</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Do you have any other comments or feedback?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please type your answer</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,143 +1037,143 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_service_forms_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_service_forms_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>experience_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>quality_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>problem_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,7 +1190,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>problem_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1319,75 +1207,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>visit_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>visit_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>visit_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>visit_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1404,7 +1292,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1415,6 +1303,431 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>recommend_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>not_sure</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>products_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>products_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>products_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>products_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>purchased_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>purchased_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>repurchase_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>repurchase_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>repurchase_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>not_sure</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>value_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>value_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>problem_customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>problem_customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>comparison_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>comparison_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>comparison_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>comparison_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>use_again_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>use_again_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>use_again_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>not_sure</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
